--- a/docs/revised_shatin/qwen3-next-80b-a3b-thinking/test_grammar_3_['No. 23_～たら〈条件(じょうけん)〉 ']_revised_revised.xlsx
+++ b/docs/revised_shatin/qwen3-next-80b-a3b-thinking/test_grammar_3_['No. 23_～たら〈条件(じょうけん)〉 ']_revised_revised.xlsx
@@ -467,20 +467,20 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 彼は（ ）日本語を勉強しています。</t>
+          <t>: もんだい1 宿題が終わったら、公園に(   )行きましょう。</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>1. いつも
-2. ときどき
-3. あまり
-4. ほとんど</t>
+          <t>1. へ
+2. に
+3. で
+4. を</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E2" s="1" t="inlineStr"/>
@@ -494,17 +494,17 @@
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : しけんが終わったら、(   )。</t>
+          <t>: もんだい1 しけんが終わったら、(   )。</t>
         </is>
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>1. 友だちと会います 2. 昼寝をします 3. 音楽を聴きます 4. 宿題をします</t>
+          <t>1. 友だちと会います 2. 昼寝をします 3. 音楽を聴きます 4. 図書館に行きます</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E3" s="1" t="inlineStr"/>
@@ -518,17 +518,17 @@
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : 家に帰ったら、(   )。</t>
+          <t>: もんだい1 家に帰ったら、(   )。</t>
         </is>
       </c>
       <c r="C4" s="1" t="inlineStr">
         <is>
-          <t>1. 休みます 2. テレビを見ます 3. 夕食を作ります 4. お風呂に入ります</t>
+          <t>1. 休みます 2. テレビを見ます 3. 夕食を作ります 4. 勉強します</t>
         </is>
       </c>
       <c r="D4" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E4" s="1" t="inlineStr"/>
@@ -542,17 +542,17 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : 本を読んだら、(   )。</t>
+          <t>: もんだい1 本を読んだら、(   )。</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>1. 感想を書きます 2. 友達に話します 3. 本を片付けます 4. 練習をします</t>
+          <t>1. 感想を書きます 2. 友達に話します 3. 本を片付けます 4. 新しい本を探します</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E5" s="1" t="inlineStr"/>
@@ -566,17 +566,17 @@
       </c>
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : 旅行が終わったら、(   )。</t>
+          <t>: もんだい1 旅行が終わったら、(   )。</t>
         </is>
       </c>
       <c r="C6" s="1" t="inlineStr">
         <is>
-          <t>1. 写真を見せます 2. お土産を渡します 3. 日記を書きます 4. 仕事に復帰します</t>
+          <t>1. 写真を見せます 2. お土産を渡します 3. 日記を書きます 4. 休みます</t>
         </is>
       </c>
       <c r="D6" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E6" s="1" t="inlineStr"/>
@@ -590,17 +590,17 @@
       </c>
       <c r="B7" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : 朝ごはんを食べたら、(   )。</t>
+          <t>: もんだい1 朝ごはんを食べたら、(   )。</t>
         </is>
       </c>
       <c r="C7" s="1" t="inlineStr">
         <is>
-          <t>1. 仕事に行きます 2. 新聞を読みます 3. 歯を磨きます 4. 学校に行きます</t>
+          <t>1. 仕事に行きます 2. 新聞を読みます 3. 歯を磨きます 4. 服を着替えます</t>
         </is>
       </c>
       <c r="D7" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E7" s="1" t="inlineStr"/>
@@ -614,17 +614,17 @@
       </c>
       <c r="B8" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : 電話が来たら、(   )。</t>
+          <t>: もんだい1 電話が来たら、(   )。</t>
         </is>
       </c>
       <c r="C8" s="1" t="inlineStr">
         <is>
-          <t>1. 出ます 2. 切ります 3. メッセージを送ります 4. かけ直します</t>
+          <t>1. 出ます 2. 切ります 3. メッセージを送ります 4. 電話を無視します</t>
         </is>
       </c>
       <c r="D8" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E8" s="1" t="inlineStr"/>
@@ -638,17 +638,17 @@
       </c>
       <c r="B9" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : 雨が降ったら、(   )。</t>
+          <t>: もんだい1 雨が降ったら、(   )。</t>
         </is>
       </c>
       <c r="C9" s="1" t="inlineStr">
         <is>
-          <t>1. 傘をさします 2. 帽子をかぶります 3. 靴を履き替えます 4. 屋内に避難します</t>
+          <t>1. 傘をさします 2. 帽子をかぶります 3. 靴を履き替えます 4. コートを着ます</t>
         </is>
       </c>
       <c r="D9" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E9" s="1" t="inlineStr"/>
@@ -662,17 +662,17 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : お金があったら、(   )。</t>
+          <t>: もんだい1 お金があったら、(   )。</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>1. 新しいカメラを買います 2. 車を修理します 3. 家を掃除します 4. 寄付をします</t>
+          <t>1. 新しいカメラを買います 2. 車を修理します 3. 家を掃除します 4. 旅行に行きます</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E10" s="1" t="inlineStr"/>
@@ -686,15 +686,12 @@
       </c>
       <c r="B11" s="1" t="inlineStr">
         <is>
-          <t>: もんだい10 今、空が（ ）。</t>
+          <t>: もんだい2 雨が降ったら、サッカーの試合は中止(   )なります。</t>
         </is>
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>1. 青い
-2. 青かった
-3. 青くない
-4. 青かった</t>
+          <t>1. に 2. で 3. を 4. が</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr">
@@ -708,25 +705,22 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Q11</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>: もんだい11 このケーキは（ ）甘いです。</t>
+          <t>: もんだい2 このボタンを 押したら、ドアが (   )。</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>1. あまり
-2. とても
-3. ちょっと
-4. ほとんど</t>
+          <t>1. 開きます 2. 開けます 3. 閉まります 4. 閉めます</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E12" s="1" t="inlineStr"/>
@@ -735,25 +729,22 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>Q12</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="B13" s="1" t="inlineStr">
         <is>
-          <t>: もんだい12 友達（ ）いっしょに旅行に行きたいです。</t>
+          <t>: もんだい2 友だちが 来たら いっしょ (   ) 食事を しましょう。</t>
         </is>
       </c>
       <c r="C13" s="1" t="inlineStr">
         <is>
-          <t>1. で
-2. と
-3. に
-4. が</t>
+          <t>1. に 2. が 3. と 4. を</t>
         </is>
       </c>
       <c r="D13" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E13" s="1" t="inlineStr"/>
@@ -762,25 +753,22 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Q13</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="B14" s="1" t="inlineStr">
         <is>
-          <t>: もんだい13 バスが（ ）ので、歩きました。</t>
+          <t>: もんだい2 かぜを ひいたら、早く 寝る (   ) いいですよ。</t>
         </is>
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>1. 来ない
-2. 来た
-3. 来ないで
-4. 来なかった</t>
+          <t>1. ほう 2. ため 3. こと 4. つもり</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E14" s="1" t="inlineStr"/>
@@ -789,25 +777,22 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>Q14</t>
+          <t>Q4</t>
         </is>
       </c>
       <c r="B15" s="1" t="inlineStr">
         <is>
-          <t>: もんだい14 この問題は（ ）難しいです。</t>
+          <t>: もんだい2 お金を ためたら、新しい パソコン (   ) 買うつもりです。</t>
         </is>
       </c>
       <c r="C15" s="1" t="inlineStr">
         <is>
-          <t>1. あまり
-2. とても
-3. ちょっと
-4. ほとんど</t>
+          <t>1. を 2. に 3. で 4. が</t>
         </is>
       </c>
       <c r="D15" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E15" s="1" t="inlineStr"/>
@@ -816,25 +801,22 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Q15</t>
+          <t>Q5</t>
         </is>
       </c>
       <c r="B16" s="1" t="inlineStr">
         <is>
-          <t>: もんだい15 明日、友達に（ ）ます。</t>
+          <t>: もんだい2 駅に 着いたら 電話 (   ) ください。</t>
         </is>
       </c>
       <c r="C16" s="1" t="inlineStr">
         <is>
-          <t>1. 会って
-2. 会い
-3. 会う
-4. 会った</t>
+          <t>1. して 2. し 3. した 4. します</t>
         </is>
       </c>
       <c r="D16" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E16" s="1" t="inlineStr"/>
@@ -843,20 +825,17 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>Q16</t>
+          <t>Q6</t>
         </is>
       </c>
       <c r="B17" s="1" t="inlineStr">
         <is>
-          <t>: もんだい16 スーパーで（ ）を買いました。</t>
+          <t>: もんだい2 もし、彼に 会えたら、この 手紙を (   )。</t>
         </is>
       </c>
       <c r="C17" s="1" t="inlineStr">
         <is>
-          <t>1. りんご
-2. りんごの
-3. りんごに
-4. りんごで</t>
+          <t>1. 渡して 2. 渡す 3. 渡し 4. 渡せ</t>
         </is>
       </c>
       <c r="D17" s="1" t="inlineStr">
@@ -870,25 +849,22 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>Q17</t>
+          <t>Q7</t>
         </is>
       </c>
       <c r="B18" s="1" t="inlineStr">
         <is>
-          <t>: もんだい17 電車が（ ）ので、遅れました。</t>
+          <t>: もんだい2 宿題が終わったら、遊びに(   )行きましょう。</t>
         </is>
       </c>
       <c r="C18" s="1" t="inlineStr">
         <is>
-          <t>1. 停まらない
-2. 停まった
-3. 停まらないで
-4. 停まらない</t>
+          <t>1. へ 2. に 3. で 4. を</t>
         </is>
       </c>
       <c r="D18" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E18" s="1" t="inlineStr"/>
@@ -897,20 +873,17 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>Q18</t>
+          <t>Q8</t>
         </is>
       </c>
       <c r="B19" s="1" t="inlineStr">
         <is>
-          <t>: もんだい18 この本は（ ）面白いです。</t>
+          <t>: もんだい2 天気が よかったら、明日 (   ) 行きます。</t>
         </is>
       </c>
       <c r="C19" s="1" t="inlineStr">
         <is>
-          <t>1. あまり
-2. とても
-3. ちょっと
-4. ほとんど</t>
+          <t>1. 海 2. 海に 3. 海で 4. 海を</t>
         </is>
       </c>
       <c r="D19" s="1" t="inlineStr">
@@ -924,25 +897,22 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>Q19</t>
+          <t>Q9</t>
         </is>
       </c>
       <c r="B20" s="1" t="inlineStr">
         <is>
-          <t>: もんだい19 公園で（ ）をしました。</t>
+          <t>: もんだい2 時間が あったら、映画を (   ) 見に行きます。</t>
         </is>
       </c>
       <c r="C20" s="1" t="inlineStr">
         <is>
-          <t>1. ランニング
-2. ランニングの
-3. ランニングに
-4. ランニングで</t>
+          <t>1. も 2. で 3. に 4. を</t>
         </is>
       </c>
       <c r="D20" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E20" s="1" t="inlineStr"/>
@@ -951,17 +921,17 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>Q20</t>
+          <t>Q10</t>
         </is>
       </c>
       <c r="B21" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい3 雨が降ったら、(   )。</t>
+          <t>: もんだい3 雨が降ったら、私は家に(   )。</t>
         </is>
       </c>
       <c r="C21" s="1" t="inlineStr">
         <is>
-          <t>1. かえります 2. かえる 3. かえりません 4. かえらない</t>
+          <t>1. 帰ります 2. 帰る 3. 帰りません 4. 帰らない</t>
         </is>
       </c>
       <c r="D21" s="1" t="inlineStr">
@@ -975,12 +945,12 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>Q21</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="B22" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい3 宿題が終わったら、(   )。</t>
+          <t>: もんだい3 宿題が終わったら、(   )。</t>
         </is>
       </c>
       <c r="C22" s="1" t="inlineStr">
@@ -999,12 +969,12 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>Q22</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="B23" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい3 お金を持っていたら、(   )。</t>
+          <t>: もんだい3 お金を持っていたら、(   )。</t>
         </is>
       </c>
       <c r="C23" s="1" t="inlineStr">
@@ -1023,12 +993,12 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Q23</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="B24" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい3 時間があったら、(   )。</t>
+          <t>: もんだい3 時間があったら、(   )。</t>
         </is>
       </c>
       <c r="C24" s="1" t="inlineStr">
@@ -1047,12 +1017,12 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>Q24</t>
+          <t>Q4</t>
         </is>
       </c>
       <c r="B25" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい3 図書館に行ったら、(   )。</t>
+          <t>: もんだい3 図書館に行ったら、(   )。</t>
         </is>
       </c>
       <c r="C25" s="1" t="inlineStr">
@@ -1071,12 +1041,12 @@
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>Q25</t>
+          <t>Q5</t>
         </is>
       </c>
       <c r="B26" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい3 友達が来たら、(   )。</t>
+          <t>: もんだい3 友達が来たら、(   )。</t>
         </is>
       </c>
       <c r="C26" s="1" t="inlineStr">
@@ -1095,12 +1065,12 @@
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>Q26</t>
+          <t>Q6</t>
         </is>
       </c>
       <c r="B27" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい3 電車が遅れたら、(   )。</t>
+          <t>: もんだい3 電車が遅れたら、(   )。</t>
         </is>
       </c>
       <c r="C27" s="1" t="inlineStr">
@@ -1119,12 +1089,12 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Q27</t>
+          <t>Q7</t>
         </is>
       </c>
       <c r="B28" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい3 映画が終わったら、(   )。</t>
+          <t>: もんだい3 映画が終わったら、(   )。</t>
         </is>
       </c>
       <c r="C28" s="1" t="inlineStr">
@@ -1143,12 +1113,12 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>Q28</t>
+          <t>Q8</t>
         </is>
       </c>
       <c r="B29" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい3 もし雨が降ったら、(   )。</t>
+          <t>: もんだい3 もし雨が降ったら、(   )。</t>
         </is>
       </c>
       <c r="C29" s="1" t="inlineStr">
@@ -1167,12 +1137,12 @@
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>Q29</t>
+          <t>Q9</t>
         </is>
       </c>
       <c r="B30" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい3 冬になったら、(   )。</t>
+          <t>: もんだい3 冬になったら、(   )。</t>
         </is>
       </c>
       <c r="C30" s="1" t="inlineStr">
@@ -1191,22 +1161,22 @@
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>Q30</t>
+          <t>Q10</t>
         </is>
       </c>
       <c r="B31" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい4 もし お金が たくさん あったら、 新しい車を (   ).</t>
+          <t>: もんだい4 もしお金がたくさんあったら、新しい車を(   )。</t>
         </is>
       </c>
       <c r="C31" s="1" t="inlineStr">
         <is>
-          <t>1. 買いたい 2. 買うことにした 3. 買うつもり 4. 買いたがっている</t>
+          <t>1. 買いたい 2. 買うつもりだ 3. 買った 4. 買うだろう</t>
         </is>
       </c>
       <c r="D31" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E31" s="1" t="inlineStr"/>
@@ -1215,12 +1185,12 @@
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>Q31</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="B32" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい4 もし 雨が 降ったら、 試合は (   ).</t>
+          <t>: もんだい4 もし 雨が 降ったら、 試合は (   ).</t>
         </is>
       </c>
       <c r="C32" s="1" t="inlineStr">
@@ -1239,12 +1209,12 @@
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>Q32</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="B33" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい4 試験が 終わったら、 わたしは 映画を 見に行く (   ).</t>
+          <t>: もんだい4 試験が 終わったら、 わたしは 映画を 見に行く (   ).</t>
         </is>
       </c>
       <c r="C33" s="1" t="inlineStr">
@@ -1263,12 +1233,12 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>Q33</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="B34" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい4 もし 暇だったら、 手伝いに (   ).</t>
+          <t>: もんだい4 もし 暇だったら、 手伝いに (   ).</t>
         </is>
       </c>
       <c r="C34" s="1" t="inlineStr">
@@ -1287,12 +1257,12 @@
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>Q34</t>
+          <t>Q4</t>
         </is>
       </c>
       <c r="B35" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい4 もし 時間が あったら、 新しいレストランで 食事を (   ).</t>
+          <t>: もんだい4 もし 時間が あったら、 新しいレストランで 食事を (   ).</t>
         </is>
       </c>
       <c r="C35" s="1" t="inlineStr">
@@ -1311,12 +1281,12 @@
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>Q35</t>
+          <t>Q5</t>
         </is>
       </c>
       <c r="B36" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい4 仕事が 終わったら、 友だちと カフェに (   ).</t>
+          <t>: もんだい4 仕事が 終わったら、 友だちと カフェに (   ).</t>
         </is>
       </c>
       <c r="C36" s="1" t="inlineStr">
@@ -1335,12 +1305,12 @@
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>Q36</t>
+          <t>Q6</t>
         </is>
       </c>
       <c r="B37" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい4 もし 試験に 合格したら、 旅行に (   ).</t>
+          <t>: もんだい4 もし 試験に 合格したら、 旅行に (   ).</t>
         </is>
       </c>
       <c r="C37" s="1" t="inlineStr">
@@ -1359,12 +1329,12 @@
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>Q37</t>
+          <t>Q7</t>
         </is>
       </c>
       <c r="B38" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい4 もし 彼が 来たら、 お祝いを (   ).</t>
+          <t>: もんだい4 もし 彼が 来たら、 お祝いを (   ).</t>
         </is>
       </c>
       <c r="C38" s="1" t="inlineStr">
@@ -1383,12 +1353,12 @@
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>Q38</t>
+          <t>Q8</t>
         </is>
       </c>
       <c r="B39" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい4 もし 間違えたら、 すぐに 先生に (   ).</t>
+          <t>: もんだい4 もし 間違えたら、 すぐに 先生に (   ).</t>
         </is>
       </c>
       <c r="C39" s="1" t="inlineStr">
@@ -1407,12 +1377,12 @@
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>Q39</t>
+          <t>Q9</t>
         </is>
       </c>
       <c r="B40" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい4 もし 彼女が 行かないなら、 わたしも 行かない (   ).</t>
+          <t>: もんだい4 もし 彼女が 行かないなら、 わたしも 行かない (   ).</t>
         </is>
       </c>
       <c r="C40" s="1" t="inlineStr">
@@ -1431,17 +1401,17 @@
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>Q40</t>
+          <t>Q10</t>
         </is>
       </c>
       <c r="B41" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい5 雨が降ったら、試合は (   )。</t>
+          <t>: もんだい5 雨が降ったら、試合は(   )。</t>
         </is>
       </c>
       <c r="C41" s="1" t="inlineStr">
         <is>
-          <t>1. 中止です 2. 中止ではない 3. 中止でした 4. 中止する</t>
+          <t>1. 中止になる 2. 中止でない 3. 中止だった 4. 中止になるだろう</t>
         </is>
       </c>
       <c r="D41" s="1" t="inlineStr">
@@ -1455,12 +1425,12 @@
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>Q41</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="B42" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい5 もし彼が来たら、私はすぐに (   )。</t>
+          <t>: もんだい5 もし彼が来たら、私はすぐに (   )。</t>
         </is>
       </c>
       <c r="C42" s="1" t="inlineStr">
@@ -1479,12 +1449,12 @@
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>Q42</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="B43" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい5 この仕事が終わったら、(   )。</t>
+          <t>: もんだい5 この仕事が終わったら、(   )。</t>
         </is>
       </c>
       <c r="C43" s="1" t="inlineStr">
@@ -1503,12 +1473,12 @@
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>Q43</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="B44" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい5 時間があったら、映画を (   )。</t>
+          <t>: もんだい5 時間があったら、映画を (   )。</t>
         </is>
       </c>
       <c r="C44" s="1" t="inlineStr">
@@ -1527,12 +1497,12 @@
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>Q44</t>
+          <t>Q4</t>
         </is>
       </c>
       <c r="B45" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい5 彼女が手伝ったら、もっと早く (   )。</t>
+          <t>: もんだい5 彼女が手伝ったら、もっと早く (   )。</t>
         </is>
       </c>
       <c r="C45" s="1" t="inlineStr">
@@ -1551,12 +1521,12 @@
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>Q45</t>
+          <t>Q5</t>
         </is>
       </c>
       <c r="B46" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい5 この本を読んだら、次に何を (   )。</t>
+          <t>: もんだい5 この本を読んだら、次に何を (   )。</t>
         </is>
       </c>
       <c r="C46" s="1" t="inlineStr">
@@ -1575,12 +1545,12 @@
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>Q46</t>
+          <t>Q6</t>
         </is>
       </c>
       <c r="B47" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい5 友達が来たら、ゲームを一緒に (   )。</t>
+          <t>: もんだい5 友達が来たら、ゲームを一緒に (   )。</t>
         </is>
       </c>
       <c r="C47" s="1" t="inlineStr">
@@ -1599,12 +1569,12 @@
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>Q47</t>
+          <t>Q7</t>
         </is>
       </c>
       <c r="B48" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい5 電車が遅れたら、授業に (   )。</t>
+          <t>: もんだい5 電車が遅れたら、授業に (   )。</t>
         </is>
       </c>
       <c r="C48" s="1" t="inlineStr">
@@ -1623,12 +1593,12 @@
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>Q48</t>
+          <t>Q8</t>
         </is>
       </c>
       <c r="B49" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい5 もしお金がたくさんあったら、旅行に (   )。</t>
+          <t>: もんだい5 もしお金がたくさんあったら、旅行に (   )。</t>
         </is>
       </c>
       <c r="C49" s="1" t="inlineStr">
@@ -1647,12 +1617,12 @@
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>Q49</t>
+          <t>Q9</t>
         </is>
       </c>
       <c r="B50" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい5 彼が答えたら、みんなが (   )。</t>
+          <t>: もんだい5 彼が答えたら、みんなが (   )。</t>
         </is>
       </c>
       <c r="C50" s="1" t="inlineStr">
@@ -1671,12 +1641,12 @@
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>Q50</t>
+          <t>Q10</t>
         </is>
       </c>
       <c r="B51" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい6 A:「雨が降ったら、どうしますか。 」 B:「雨が降ったら、家で映画を(   )。 」</t>
+          <t>: もんだい6 A:「雨が降ったら、どうしますか。」 B:「雨が降ったら、家で映画を(   )。」</t>
         </is>
       </c>
       <c r="C51" s="1" t="inlineStr">
@@ -1695,12 +1665,12 @@
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>Q51</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="B52" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい6 A:「もし道に迷ったら、どうしますか。 」 B:「すぐにアプリで(   )。 」</t>
+          <t>: もんだい6 A:「もし道に迷ったら、どうしますか。 」 B:「すぐにアプリで(   )。 」</t>
         </is>
       </c>
       <c r="C52" s="1" t="inlineStr">
@@ -1719,12 +1689,12 @@
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>Q52</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="B53" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい6 A:「テストが終わったら、何をしますか。 」 B:「終わったら、友達とカフェに(   )。 」</t>
+          <t>: もんだい6 A:「テストが終わったら、何をしますか。 」 B:「終わったら、友達とカフェに(   )。 」</t>
         </is>
       </c>
       <c r="C53" s="1" t="inlineStr">
@@ -1743,12 +1713,12 @@
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>Q53</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="B54" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい6 A:「明日暇(ひま)だったら、何をしますか。 」 B:「暇だったら、家でゆっくり(   )。 」</t>
+          <t>: もんだい6 A:「明日暇(ひま)だったら、何をしますか。 」 B:「暇だったら、家でゆっくり(   )。 」</t>
         </is>
       </c>
       <c r="C54" s="1" t="inlineStr">
@@ -1767,12 +1737,12 @@
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>Q54</t>
+          <t>Q4</t>
         </is>
       </c>
       <c r="B55" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい6 A:「もし、時間があったら、手伝ってもらえますか。 」 B:「時間があったら、もちろん(   )。 」</t>
+          <t>: もんだい6 A:「もし、時間があったら、手伝ってもらえますか。 」 B:「時間があったら、もちろん(   )。 」</t>
         </is>
       </c>
       <c r="C55" s="1" t="inlineStr">
@@ -1791,12 +1761,12 @@
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>Q55</t>
+          <t>Q5</t>
         </is>
       </c>
       <c r="B56" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい6 A:「もし、今週末に予定がなかったら、どこに行きたいですか。 」 B:「予定がなかったら、海に(   )。 」</t>
+          <t>: もんだい6 A:「もし、今週末に予定がなかったら、どこに行きたいですか。 」 B:「予定がなかったら、海に(   )。 」</t>
         </is>
       </c>
       <c r="C56" s="1" t="inlineStr">
@@ -1815,12 +1785,12 @@
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>Q56</t>
+          <t>Q6</t>
         </is>
       </c>
       <c r="B57" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい6 A:「バスが遅れたら、どうしますか。 」 B:「遅れたら、タクシーを(   )。 」</t>
+          <t>: もんだい6 A:「バスが遅れたら、どうしますか。 」 B:「遅れたら、タクシーを(   )。 」</t>
         </is>
       </c>
       <c r="C57" s="1" t="inlineStr">
@@ -1839,12 +1809,12 @@
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>Q57</t>
+          <t>Q7</t>
         </is>
       </c>
       <c r="B58" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい6 A:「もし、財布を忘れたら、どうしますか。 」 B:「忘れたら、友達に(   )。 」</t>
+          <t>: もんだい6 A:「もし、財布を忘れたら、どうしますか。 」 B:「忘れたら、友達に(   )。 」</t>
         </is>
       </c>
       <c r="C58" s="1" t="inlineStr">
@@ -1863,12 +1833,12 @@
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>Q58</t>
+          <t>Q8</t>
         </is>
       </c>
       <c r="B59" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい6 A:「もし、雨が降ったら、ピクニックはどうしますか。 」 B:「雨が降ったら、ピクニックは(   )。 」</t>
+          <t>: もんだい6 A:「もし、雨が降ったら、ピクニックはどうしますか。 」 B:「雨が降ったら、ピクニックは(   )。 」</t>
         </is>
       </c>
       <c r="C59" s="1" t="inlineStr">
@@ -1887,12 +1857,12 @@
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>Q59</t>
+          <t>Q9</t>
         </is>
       </c>
       <c r="B60" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい6 A:「試験に合格したら、何をしますか。 」 B:「合格したら、家族と(   )。 」</t>
+          <t>: もんだい6 A:「試験に合格したら、何をしますか。 」 B:「合格したら、家族と(   )。 」</t>
         </is>
       </c>
       <c r="C60" s="1" t="inlineStr">
@@ -1911,22 +1881,22 @@
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>Q60</t>
+          <t>Q10</t>
         </is>
       </c>
       <c r="B61" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい7 もし 雨が 降ったら (   )。</t>
+          <t>: もんだい7 もし雨が降ったら、(   )。</t>
         </is>
       </c>
       <c r="C61" s="1" t="inlineStr">
         <is>
-          <t>1. 行ける 2. 行けない 3. 行こう 4. 行く</t>
+          <t>1. 行きます 2. 行かない 3. 行こう 4. 行く</t>
         </is>
       </c>
       <c r="D61" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E61" s="1" t="inlineStr"/>
@@ -1935,12 +1905,12 @@
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>Q61</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="B62" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい7 テストが 終わったら (   )。</t>
+          <t>: もんだい7 テストが 終わったら (   )。</t>
         </is>
       </c>
       <c r="C62" s="1" t="inlineStr">
@@ -1959,12 +1929,12 @@
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>Q62</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="B63" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい7 もし お金が あったら、(   )。</t>
+          <t>: もんだい7 もし お金が あったら、(   )。</t>
         </is>
       </c>
       <c r="C63" s="1" t="inlineStr">
@@ -1983,12 +1953,12 @@
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>Q63</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="B64" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい7 時間が あったら (   )。</t>
+          <t>: もんだい7 時間が あったら (   )。</t>
         </is>
       </c>
       <c r="C64" s="1" t="inlineStr">
@@ -2007,12 +1977,12 @@
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>Q64</t>
+          <t>Q4</t>
         </is>
       </c>
       <c r="B65" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい7 もし 彼が 来たら、(   )。</t>
+          <t>: もんだい7 もし 彼が 来たら、(   )。</t>
         </is>
       </c>
       <c r="C65" s="1" t="inlineStr">
@@ -2031,12 +2001,12 @@
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>Q65</t>
+          <t>Q5</t>
         </is>
       </c>
       <c r="B66" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい7 パーティーが 終わったら (   )。</t>
+          <t>: もんだい7 パーティーが 終わったら (   )。</t>
         </is>
       </c>
       <c r="C66" s="1" t="inlineStr">
@@ -2055,12 +2025,12 @@
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>Q66</t>
+          <t>Q6</t>
         </is>
       </c>
       <c r="B67" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい7 彼女が 行くと 言ったら、(   )。</t>
+          <t>: もんだい7 彼女が 行くと 言ったら、(   )。</t>
         </is>
       </c>
       <c r="C67" s="1" t="inlineStr">
@@ -2079,12 +2049,12 @@
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>Q67</t>
+          <t>Q7</t>
         </is>
       </c>
       <c r="B68" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい7 もし 道が わからなかったら、(   )。</t>
+          <t>: もんだい7 もし 道が わからなかったら、(   )。</t>
         </is>
       </c>
       <c r="C68" s="1" t="inlineStr">
@@ -2103,12 +2073,12 @@
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>Q68</t>
+          <t>Q8</t>
         </is>
       </c>
       <c r="B69" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい7 天気が よかったら、(   )。</t>
+          <t>: もんだい7 天気が よかったら、(   )。</t>
         </is>
       </c>
       <c r="C69" s="1" t="inlineStr">
@@ -2127,12 +2097,12 @@
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>Q69</t>
+          <t>Q9</t>
         </is>
       </c>
       <c r="B70" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい7 先生が 来たら、(   )。</t>
+          <t>: もんだい7 先生が 来たら、(   )。</t>
         </is>
       </c>
       <c r="C70" s="1" t="inlineStr">
@@ -2151,22 +2121,22 @@
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>Q70</t>
+          <t>Q10</t>
         </is>
       </c>
       <c r="B71" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい8 雨が降ったら、試合は(   )中止(ちゅうし)になります。</t>
+          <t>: もんだい8 雨が降ったら、試合は(   )中止(ちゅうし)になります。</t>
         </is>
       </c>
       <c r="C71" s="1" t="inlineStr">
         <is>
-          <t>1. ように 2. みたいに 3. ほどに 4. らしく</t>
+          <t>1. たぶん 2. きっと 3. ように 4. おそらく</t>
         </is>
       </c>
       <c r="D71" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E71" s="1" t="inlineStr"/>
@@ -2175,12 +2145,12 @@
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>Q71</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="B72" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい8 このケーキを食べたら、まるで天国(てんごく)にいる(   )美味(おい)しさです。</t>
+          <t>: もんだい8 このケーキを食べたら、まるで天国(てんごく)にいる(   )美味(おい)しさです。</t>
         </is>
       </c>
       <c r="C72" s="1" t="inlineStr">
@@ -2199,12 +2169,12 @@
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>Q72</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="B73" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい8 彼女(かのじょ)が来たら、部屋(へや)が明るくなった(   )感じ(かんじ)です。</t>
+          <t>: もんだい8 彼女(かのじょ)が来たら、部屋(へや)が明るくなった(   )感じ(かんじ)です。</t>
         </is>
       </c>
       <c r="C73" s="1" t="inlineStr">
@@ -2223,12 +2193,12 @@
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>Q73</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="B74" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい8 食事(しょくじ)が終わったら、(   )映画(えいが)を見に行きましょう。</t>
+          <t>: もんだい8 食事(しょくじ)が終わったら、(   )映画(えいが)を見に行きましょう。</t>
         </is>
       </c>
       <c r="C74" s="1" t="inlineStr">
@@ -2247,12 +2217,12 @@
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>Q74</t>
+          <t>Q4</t>
         </is>
       </c>
       <c r="B75" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい8 彼(かれ)の話(はなし)を聞いたら、夢(ゆめ)を見ている(   )気分(きぶん)になりました。</t>
+          <t>: もんだい8 彼(かれ)の話(はなし)を聞いたら、夢(ゆめ)を見ている(   )気分(きぶん)になりました。</t>
         </is>
       </c>
       <c r="C75" s="1" t="inlineStr">
@@ -2271,12 +2241,12 @@
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>Q75</t>
+          <t>Q5</t>
         </is>
       </c>
       <c r="B76" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい8 お金(かね)があったら、まるで王様(おうさま)の(   )生活(せいかつ)ができるでしょう。</t>
+          <t>: もんだい8 お金(かね)があったら、まるで王様(おうさま)の(   )生活(せいかつ)ができるでしょう。</t>
         </is>
       </c>
       <c r="C76" s="1" t="inlineStr">
@@ -2295,12 +2265,12 @@
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>Q76</t>
+          <t>Q6</t>
         </is>
       </c>
       <c r="B77" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい8 宿題(しゅくだい)が終わったら、(   )遊(あそ)びに行けます。</t>
+          <t>: もんだい8 宿題(しゅくだい)が終わったら、(   )遊(あそ)びに行けます。</t>
         </is>
       </c>
       <c r="C77" s="1" t="inlineStr">
@@ -2319,12 +2289,12 @@
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>Q77</t>
+          <t>Q7</t>
         </is>
       </c>
       <c r="B78" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい8 彼(かれ)は試験(しけん)に合格(ごうかく)したら、(   )喜(よろこ)びました。</t>
+          <t>: もんだい8 彼(かれ)は試験(しけん)に合格(ごうかく)したら、(   )喜(よろこ)びました。</t>
         </is>
       </c>
       <c r="C78" s="1" t="inlineStr">
@@ -2343,12 +2313,12 @@
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>Q78</t>
+          <t>Q8</t>
         </is>
       </c>
       <c r="B79" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい8 もし雨(あめ)が降ったら、(   )家(いえ)に帰(かえ)ります。</t>
+          <t>: もんだい8 もし雨(あめ)が降ったら、(   )家(いえ)に帰(かえ)ります。</t>
         </is>
       </c>
       <c r="C79" s="1" t="inlineStr">
@@ -2367,12 +2337,12 @@
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>Q79</t>
+          <t>Q9</t>
         </is>
       </c>
       <c r="B80" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい8 彼女(かのじょ)が笑(わら)ったら、太陽(たいよう)が輝(かがや)く(   )明(あか)るいです。</t>
+          <t>: もんだい8 彼女(かのじょ)が笑(わら)ったら、太陽(たいよう)が輝(かがや)く(   )明(あか)るいです。</t>
         </is>
       </c>
       <c r="C80" s="1" t="inlineStr">

--- a/docs/revised_shatin/qwen3-next-80b-a3b-thinking/test_grammar_3_['No. 23_～たら〈条件(じょうけん)〉 ']_revised_revised.xlsx
+++ b/docs/revised_shatin/qwen3-next-80b-a3b-thinking/test_grammar_3_['No. 23_～たら〈条件(じょうけん)〉 ']_revised_revised.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F80"/>
+  <dimension ref="A1:F81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -467,20 +467,17 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 宿題が終わったら、公園に(   )行きましょう。</t>
+          <t>: もんだい1雨がやんだら、(   )。</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>1. へ
-2. に
-3. で
-4. を</t>
+          <t>1. さんぽに行きます 2. うちに帰ります 3. テレビを見ます 4. 本を読みます</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E2" s="1" t="inlineStr"/>
@@ -494,12 +491,12 @@
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 しけんが終わったら、(   )。</t>
+          <t>: もんだい1もし時間があったら、(   )。</t>
         </is>
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>1. 友だちと会います 2. 昼寝をします 3. 音楽を聴きます 4. 図書館に行きます</t>
+          <t>1. 映画を見ます 2. 買い物をします 3. 散歩に行きます 4. 料理をします</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr">
@@ -518,12 +515,12 @@
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 家に帰ったら、(   )。</t>
+          <t>: もんだい1しけんが終わったら、(   )。</t>
         </is>
       </c>
       <c r="C4" s="1" t="inlineStr">
         <is>
-          <t>1. 休みます 2. テレビを見ます 3. 夕食を作ります 4. 勉強します</t>
+          <t>1. 友だちと会います 2. 昼寝をします 3. 音楽を聴きます 4. 図書館に行きます</t>
         </is>
       </c>
       <c r="D4" s="1" t="inlineStr">
@@ -542,12 +539,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 本を読んだら、(   )。</t>
+          <t>: もんだい1家に帰ったら、(   )。</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>1. 感想を書きます 2. 友達に話します 3. 本を片付けます 4. 新しい本を探します</t>
+          <t>1. 休みます 2. テレビを見ます 3. 夕食を作ります 4. 勉強します</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr">
@@ -566,12 +563,12 @@
       </c>
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 旅行が終わったら、(   )。</t>
+          <t>: もんだい1本を読んだら、(   )。</t>
         </is>
       </c>
       <c r="C6" s="1" t="inlineStr">
         <is>
-          <t>1. 写真を見せます 2. お土産を渡します 3. 日記を書きます 4. 休みます</t>
+          <t>1. 感想を書きます 2. 友達に話します 3. 本を片付けます 4. 新しい本を探します</t>
         </is>
       </c>
       <c r="D6" s="1" t="inlineStr">
@@ -590,12 +587,12 @@
       </c>
       <c r="B7" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 朝ごはんを食べたら、(   )。</t>
+          <t>: もんだい1旅行が終わったら、(   )。</t>
         </is>
       </c>
       <c r="C7" s="1" t="inlineStr">
         <is>
-          <t>1. 仕事に行きます 2. 新聞を読みます 3. 歯を磨きます 4. 服を着替えます</t>
+          <t>1. 写真を見せます 2. お土産を渡します 3. 日記を書きます 4. 休みます</t>
         </is>
       </c>
       <c r="D7" s="1" t="inlineStr">
@@ -614,12 +611,12 @@
       </c>
       <c r="B8" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 電話が来たら、(   )。</t>
+          <t>: もんだい1朝ごはんを食べたら、(   )。</t>
         </is>
       </c>
       <c r="C8" s="1" t="inlineStr">
         <is>
-          <t>1. 出ます 2. 切ります 3. メッセージを送ります 4. 電話を無視します</t>
+          <t>1. 仕事に行きます 2. 新聞を読みます 3. 歯を磨きます 4. 服を着替えます</t>
         </is>
       </c>
       <c r="D8" s="1" t="inlineStr">
@@ -638,12 +635,12 @@
       </c>
       <c r="B9" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 雨が降ったら、(   )。</t>
+          <t>: もんだい1電話が来たら、(   )。</t>
         </is>
       </c>
       <c r="C9" s="1" t="inlineStr">
         <is>
-          <t>1. 傘をさします 2. 帽子をかぶります 3. 靴を履き替えます 4. コートを着ます</t>
+          <t>1. 出ます 2. 切ります 3. メッセージを送ります 4. 電話を無視します</t>
         </is>
       </c>
       <c r="D9" s="1" t="inlineStr">
@@ -662,12 +659,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 お金があったら、(   )。</t>
+          <t>: もんだい1雨が降ったら、(   )。</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>1. 新しいカメラを買います 2. 車を修理します 3. 家を掃除します 4. 旅行に行きます</t>
+          <t>1. 傘をさします 2. 帽子をかぶります 3. 靴を履き替えます 4. コートを着ます</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr">
@@ -686,12 +683,12 @@
       </c>
       <c r="B11" s="1" t="inlineStr">
         <is>
-          <t>: もんだい2 雨が降ったら、サッカーの試合は中止(   )なります。</t>
+          <t>: もんだい1お金があったら、(   )。</t>
         </is>
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>1. に 2. で 3. を 4. が</t>
+          <t>1. 新しいカメラを買います 2. 車を修理します 3. 家を掃除します 4. 旅行に行きます</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr">
@@ -710,12 +707,12 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>: もんだい2 このボタンを 押したら、ドアが (   )。</t>
+          <t>: もんだい2雨が ふったら サッカーの試合は 中止 (   ) なる。</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>1. 開きます 2. 開けます 3. 閉まります 4. 閉めます</t>
+          <t>1. に 2. で 3. を 4. が</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr">
@@ -734,17 +731,17 @@
       </c>
       <c r="B13" s="1" t="inlineStr">
         <is>
-          <t>: もんだい2 友だちが 来たら いっしょ (   ) 食事を しましょう。</t>
+          <t>: もんだい2このボタンを 押したら、ドアが (   )。</t>
         </is>
       </c>
       <c r="C13" s="1" t="inlineStr">
         <is>
-          <t>1. に 2. が 3. と 4. を</t>
+          <t>1. 開きます 2. 開けます 3. 閉まります 4. 閉めます</t>
         </is>
       </c>
       <c r="D13" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E13" s="1" t="inlineStr"/>
@@ -758,17 +755,17 @@
       </c>
       <c r="B14" s="1" t="inlineStr">
         <is>
-          <t>: もんだい2 かぜを ひいたら、早く 寝る (   ) いいですよ。</t>
+          <t>: もんだい2友だちが 来たら いっしょ (   ) 食事を しましょう。</t>
         </is>
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>1. ほう 2. ため 3. こと 4. つもり</t>
+          <t>1. に 2. が 3. と 4. を</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E14" s="1" t="inlineStr"/>
@@ -782,12 +779,12 @@
       </c>
       <c r="B15" s="1" t="inlineStr">
         <is>
-          <t>: もんだい2 お金を ためたら、新しい パソコン (   ) 買うつもりです。</t>
+          <t>: もんだい2かぜを ひいたら、早く 寝る (   ) いいですよ。</t>
         </is>
       </c>
       <c r="C15" s="1" t="inlineStr">
         <is>
-          <t>1. を 2. に 3. で 4. が</t>
+          <t>1. ほう 2. ため 3. こと 4. つもり</t>
         </is>
       </c>
       <c r="D15" s="1" t="inlineStr">
@@ -806,12 +803,12 @@
       </c>
       <c r="B16" s="1" t="inlineStr">
         <is>
-          <t>: もんだい2 駅に 着いたら 電話 (   ) ください。</t>
+          <t>: もんだい2お金を ためたら、新しい パソコン (   ) 買うつもりです。</t>
         </is>
       </c>
       <c r="C16" s="1" t="inlineStr">
         <is>
-          <t>1. して 2. し 3. した 4. します</t>
+          <t>1. を 2. に 3. で 4. が</t>
         </is>
       </c>
       <c r="D16" s="1" t="inlineStr">
@@ -830,12 +827,12 @@
       </c>
       <c r="B17" s="1" t="inlineStr">
         <is>
-          <t>: もんだい2 もし、彼に 会えたら、この 手紙を (   )。</t>
+          <t>: もんだい2駅に 着いたら 電話 (   ) ください。</t>
         </is>
       </c>
       <c r="C17" s="1" t="inlineStr">
         <is>
-          <t>1. 渡して 2. 渡す 3. 渡し 4. 渡せ</t>
+          <t>1. して 2. し 3. した 4. します</t>
         </is>
       </c>
       <c r="D17" s="1" t="inlineStr">
@@ -854,12 +851,12 @@
       </c>
       <c r="B18" s="1" t="inlineStr">
         <is>
-          <t>: もんだい2 宿題が終わったら、遊びに(   )行きましょう。</t>
+          <t>: もんだい2もし、彼に 会えたら、この 手紙を (   )。</t>
         </is>
       </c>
       <c r="C18" s="1" t="inlineStr">
         <is>
-          <t>1. へ 2. に 3. で 4. を</t>
+          <t>1. 渡して 2. 渡す 3. 渡し 4. 渡せ</t>
         </is>
       </c>
       <c r="D18" s="1" t="inlineStr">
@@ -878,17 +875,17 @@
       </c>
       <c r="B19" s="1" t="inlineStr">
         <is>
-          <t>: もんだい2 天気が よかったら、明日 (   ) 行きます。</t>
+          <t>: もんだい2宿題が 終わったら、遊びに (   ) 行きましょう。</t>
         </is>
       </c>
       <c r="C19" s="1" t="inlineStr">
         <is>
-          <t>1. 海 2. 海に 3. 海で 4. 海を</t>
+          <t>1. に 2. で 3. を 4. へ</t>
         </is>
       </c>
       <c r="D19" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E19" s="1" t="inlineStr"/>
@@ -902,17 +899,17 @@
       </c>
       <c r="B20" s="1" t="inlineStr">
         <is>
-          <t>: もんだい2 時間が あったら、映画を (   ) 見に行きます。</t>
+          <t>: もんだい2天気が よかったら、明日 (   ) 行きます。</t>
         </is>
       </c>
       <c r="C20" s="1" t="inlineStr">
         <is>
-          <t>1. も 2. で 3. に 4. を</t>
+          <t>1. 海 2. 海に 3. 海で 4. 海を</t>
         </is>
       </c>
       <c r="D20" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E20" s="1" t="inlineStr"/>
@@ -926,17 +923,17 @@
       </c>
       <c r="B21" s="1" t="inlineStr">
         <is>
-          <t>: もんだい3 雨が降ったら、私は家に(   )。</t>
+          <t>: もんだい2時間が あったら、映画を (   ) 見に行きます。</t>
         </is>
       </c>
       <c r="C21" s="1" t="inlineStr">
         <is>
-          <t>1. 帰ります 2. 帰る 3. 帰りません 4. 帰らない</t>
+          <t>1. も 2. で 3. に 4. を</t>
         </is>
       </c>
       <c r="D21" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E21" s="1" t="inlineStr"/>
@@ -950,12 +947,12 @@
       </c>
       <c r="B22" s="1" t="inlineStr">
         <is>
-          <t>: もんだい3 宿題が終わったら、(   )。</t>
+          <t>: もんだい3雨が降ったら、(   )。</t>
         </is>
       </c>
       <c r="C22" s="1" t="inlineStr">
         <is>
-          <t>1. あそびます 2. あそんで 3. あそばない 4. あそびません</t>
+          <t>1. かえります 2. かえる 3. かえりません 4. かえらない</t>
         </is>
       </c>
       <c r="D22" s="1" t="inlineStr">
@@ -974,12 +971,12 @@
       </c>
       <c r="B23" s="1" t="inlineStr">
         <is>
-          <t>: もんだい3 お金を持っていたら、(   )。</t>
+          <t>: もんだい3宿題が終わったら、(   )。</t>
         </is>
       </c>
       <c r="C23" s="1" t="inlineStr">
         <is>
-          <t>1. 買います 2. 買いません 3. 買う 4. 買わない</t>
+          <t>1. あそびます 2. あそんで 3. あそばない 4. あそびません</t>
         </is>
       </c>
       <c r="D23" s="1" t="inlineStr">
@@ -998,12 +995,12 @@
       </c>
       <c r="B24" s="1" t="inlineStr">
         <is>
-          <t>: もんだい3 時間があったら、(   )。</t>
+          <t>: もんだい3お金を持っていたら、(   )。</t>
         </is>
       </c>
       <c r="C24" s="1" t="inlineStr">
         <is>
-          <t>1. でかけます 2. でかけない 3. でかけません 4. でかける</t>
+          <t>1. 買います 2. 買いません 3. 買う 4. 買わない</t>
         </is>
       </c>
       <c r="D24" s="1" t="inlineStr">
@@ -1022,12 +1019,12 @@
       </c>
       <c r="B25" s="1" t="inlineStr">
         <is>
-          <t>: もんだい3 図書館に行ったら、(   )。</t>
+          <t>: もんだい3時間があったら、(   )。</t>
         </is>
       </c>
       <c r="C25" s="1" t="inlineStr">
         <is>
-          <t>1. 本を借ります 2. 本を読む 3. 本を探す 4. 本を返す</t>
+          <t>1. でかけます 2. でかけない 3. でかけません 4. でかける</t>
         </is>
       </c>
       <c r="D25" s="1" t="inlineStr">
@@ -1046,12 +1043,12 @@
       </c>
       <c r="B26" s="1" t="inlineStr">
         <is>
-          <t>: もんだい3 友達が来たら、(   )。</t>
+          <t>: もんだい3図書館に行ったら、(   )。</t>
         </is>
       </c>
       <c r="C26" s="1" t="inlineStr">
         <is>
-          <t>1. パーティーをします 2. 話をします 3. 一緒に遊びます 4. お茶を飲みます</t>
+          <t>1. 本を借ります 2. 本を読む 3. 本を探す 4. 本を返す</t>
         </is>
       </c>
       <c r="D26" s="1" t="inlineStr">
@@ -1070,12 +1067,12 @@
       </c>
       <c r="B27" s="1" t="inlineStr">
         <is>
-          <t>: もんだい3 電車が遅れたら、(   )。</t>
+          <t>: もんだい3友達が来たら、(   )。</t>
         </is>
       </c>
       <c r="C27" s="1" t="inlineStr">
         <is>
-          <t>1. ちこくします 2. ちこくする 3. ちこくしない 4. ちこくしません</t>
+          <t>1. パーティーをします 2. 話をします 3. 一緒に遊びます 4. お茶を飲みます</t>
         </is>
       </c>
       <c r="D27" s="1" t="inlineStr">
@@ -1094,12 +1091,12 @@
       </c>
       <c r="B28" s="1" t="inlineStr">
         <is>
-          <t>: もんだい3 映画が終わったら、(   )。</t>
+          <t>: もんだい3電車が遅れたら、(   )。</t>
         </is>
       </c>
       <c r="C28" s="1" t="inlineStr">
         <is>
-          <t>1. かえります 2. ご飯を食べます 3. 散歩します 4. カフェに行きます</t>
+          <t>1. ちこくします 2. ちこくする 3. ちこくしない 4. ちこくしません</t>
         </is>
       </c>
       <c r="D28" s="1" t="inlineStr">
@@ -1118,12 +1115,12 @@
       </c>
       <c r="B29" s="1" t="inlineStr">
         <is>
-          <t>: もんだい3 もし雨が降ったら、(   )。</t>
+          <t>: もんだい3映画が終わったら、(   )。</t>
         </is>
       </c>
       <c r="C29" s="1" t="inlineStr">
         <is>
-          <t>1. 傘をさします 2. 雨宿りします 3. 帰ります 4. 走ります</t>
+          <t>1. かえります 2. ご飯を食べます 3. 散歩します 4. カフェに行きます</t>
         </is>
       </c>
       <c r="D29" s="1" t="inlineStr">
@@ -1142,12 +1139,12 @@
       </c>
       <c r="B30" s="1" t="inlineStr">
         <is>
-          <t>: もんだい3 冬になったら、(   )。</t>
+          <t>: もんだい3もし雨が降ったら、(   )。</t>
         </is>
       </c>
       <c r="C30" s="1" t="inlineStr">
         <is>
-          <t>1. さむくなります 2. コートを着ます 3. スキーをします 4. 暖房を使います</t>
+          <t>1. 傘をさします 2. 雨宿りします 3. 帰ります 4. 走ります</t>
         </is>
       </c>
       <c r="D30" s="1" t="inlineStr">
@@ -1166,17 +1163,17 @@
       </c>
       <c r="B31" s="1" t="inlineStr">
         <is>
-          <t>: もんだい4 もしお金がたくさんあったら、新しい車を(   )。</t>
+          <t>: もんだい3冬になったら、(   )。</t>
         </is>
       </c>
       <c r="C31" s="1" t="inlineStr">
         <is>
-          <t>1. 買いたい 2. 買うつもりだ 3. 買った 4. 買うだろう</t>
+          <t>1. さむくなります 2. コートを着ます 3. スキーをします 4. 暖房を使います</t>
         </is>
       </c>
       <c r="D31" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E31" s="1" t="inlineStr"/>
@@ -1190,17 +1187,17 @@
       </c>
       <c r="B32" s="1" t="inlineStr">
         <is>
-          <t>: もんだい4 もし 雨が 降ったら、 試合は (   ).</t>
+          <t>: もんだい4もし お金が たくさん あったら、 新しい車を (   ).</t>
         </is>
       </c>
       <c r="C32" s="1" t="inlineStr">
         <is>
-          <t>1. 中止する 2. 中止したい 3. 中止するかもしれない 4. 中止した</t>
+          <t>1. 買いたい 2. 買うことにした 3. 買うつもり 4. 買いたがっている</t>
         </is>
       </c>
       <c r="D32" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E32" s="1" t="inlineStr"/>
@@ -1214,17 +1211,17 @@
       </c>
       <c r="B33" s="1" t="inlineStr">
         <is>
-          <t>: もんだい4 試験が 終わったら、 わたしは 映画を 見に行く (   ).</t>
+          <t>: もんだい4もし 雨が 降ったら、 試合は (   ).</t>
         </is>
       </c>
       <c r="C33" s="1" t="inlineStr">
         <is>
-          <t>1. つもりだ 2. そうだ 3. ところだ 4. らしい</t>
+          <t>1. 中止する 2. 中止したい 3. 中止するかもしれない 4. 中止した</t>
         </is>
       </c>
       <c r="D33" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E33" s="1" t="inlineStr"/>
@@ -1238,17 +1235,17 @@
       </c>
       <c r="B34" s="1" t="inlineStr">
         <is>
-          <t>: もんだい4 もし 暇だったら、 手伝いに (   ).</t>
+          <t>: もんだい4試験が 終わったら、 わたしは 映画を 見に行く (   ).</t>
         </is>
       </c>
       <c r="C34" s="1" t="inlineStr">
         <is>
-          <t>1. 行くことにする 2. 行くかもしれない 3. 行くつもり 4. 行きたがる</t>
+          <t>1. つもりだ 2. そうだ 3. ところだ 4. らしい</t>
         </is>
       </c>
       <c r="D34" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E34" s="1" t="inlineStr"/>
@@ -1262,12 +1259,12 @@
       </c>
       <c r="B35" s="1" t="inlineStr">
         <is>
-          <t>: もんだい4 もし 時間が あったら、 新しいレストランで 食事を (   ).</t>
+          <t>: もんだい4もし 暇だったら、 手伝いに (   ).</t>
         </is>
       </c>
       <c r="C35" s="1" t="inlineStr">
         <is>
-          <t>1. することにした 2. したい 3. したがっている 4. するらしい</t>
+          <t>1. 行くことにする 2. 行くかもしれない 3. 行くつもり 4. 行きたがる</t>
         </is>
       </c>
       <c r="D35" s="1" t="inlineStr">
@@ -1286,17 +1283,17 @@
       </c>
       <c r="B36" s="1" t="inlineStr">
         <is>
-          <t>: もんだい4 仕事が 終わったら、 友だちと カフェに (   ).</t>
+          <t>: もんだい4もし 時間が あったら、 新しいレストランで 食事を (   ).</t>
         </is>
       </c>
       <c r="C36" s="1" t="inlineStr">
         <is>
-          <t>1. 行くことにした 2. 行きたい 3. 行くかもしれない 4. 行った</t>
+          <t>1. することにした 2. したい 3. したがっている 4. するらしい</t>
         </is>
       </c>
       <c r="D36" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E36" s="1" t="inlineStr"/>
@@ -1310,12 +1307,12 @@
       </c>
       <c r="B37" s="1" t="inlineStr">
         <is>
-          <t>: もんだい4 もし 試験に 合格したら、 旅行に (   ).</t>
+          <t>: もんだい4仕事が 終わったら、 友だちと カフェに (   ).</t>
         </is>
       </c>
       <c r="C37" s="1" t="inlineStr">
         <is>
-          <t>1. 行くつもりだ 2. 行ったら 3. 行くらしい 4. 行きたい</t>
+          <t>1. 行くことにした 2. 行きたい 3. 行くかもしれない 4. 行った</t>
         </is>
       </c>
       <c r="D37" s="1" t="inlineStr">
@@ -1334,12 +1331,12 @@
       </c>
       <c r="B38" s="1" t="inlineStr">
         <is>
-          <t>: もんだい4 もし 彼が 来たら、 お祝いを (   ).</t>
+          <t>: もんだい4もし 試験に 合格したら、 旅行に (   ).</t>
         </is>
       </c>
       <c r="C38" s="1" t="inlineStr">
         <is>
-          <t>1. することにする 2. したがる 3. したい 4. するらしい</t>
+          <t>1. 行くつもりだ 2. 行ったら 3. 行くらしい 4. 行きたい</t>
         </is>
       </c>
       <c r="D38" s="1" t="inlineStr">
@@ -1358,17 +1355,17 @@
       </c>
       <c r="B39" s="1" t="inlineStr">
         <is>
-          <t>: もんだい4 もし 間違えたら、 すぐに 先生に (   ).</t>
+          <t>: もんだい4もし 彼が 来たら、 お祝いを (   ).</t>
         </is>
       </c>
       <c r="C39" s="1" t="inlineStr">
         <is>
-          <t>1. 聞くことにした 2. 聞きたがる 3. 聞くつもりだ 4. 聞いた</t>
+          <t>1. することにする 2. したがる 3. したい 4. するらしい</t>
         </is>
       </c>
       <c r="D39" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E39" s="1" t="inlineStr"/>
@@ -1382,17 +1379,17 @@
       </c>
       <c r="B40" s="1" t="inlineStr">
         <is>
-          <t>: もんだい4 もし 彼女が 行かないなら、 わたしも 行かない (   ).</t>
+          <t>: もんだい4もし 間違えたら、 すぐに 先生に (   ).</t>
         </is>
       </c>
       <c r="C40" s="1" t="inlineStr">
         <is>
-          <t>1. ことにした 2. かもしれない 3. つもりだ 4. そうだ</t>
+          <t>1. 聞くことにした 2. 聞きたがる 3. 聞くつもりだ 4. 聞いた</t>
         </is>
       </c>
       <c r="D40" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E40" s="1" t="inlineStr"/>
@@ -1406,12 +1403,12 @@
       </c>
       <c r="B41" s="1" t="inlineStr">
         <is>
-          <t>: もんだい5 雨が降ったら、試合は(   )。</t>
+          <t>: もんだい4もし 彼女が 行かないなら、 わたしも 行かない (   ).</t>
         </is>
       </c>
       <c r="C41" s="1" t="inlineStr">
         <is>
-          <t>1. 中止になる 2. 中止でない 3. 中止だった 4. 中止になるだろう</t>
+          <t>1. ことにした 2. かもしれない 3. つもりだ 4. そうだ</t>
         </is>
       </c>
       <c r="D41" s="1" t="inlineStr">
@@ -1430,12 +1427,12 @@
       </c>
       <c r="B42" s="1" t="inlineStr">
         <is>
-          <t>: もんだい5 もし彼が来たら、私はすぐに (   )。</t>
+          <t>: もんだい5雨が降ったら、試合は (   )。</t>
         </is>
       </c>
       <c r="C42" s="1" t="inlineStr">
         <is>
-          <t>1. 行きます 2. 準備します 3. 話します 4. 迎えます</t>
+          <t>1. 中止です 2. 中止ではない 3. 中止でした 4. 中止する</t>
         </is>
       </c>
       <c r="D42" s="1" t="inlineStr">
@@ -1454,12 +1451,12 @@
       </c>
       <c r="B43" s="1" t="inlineStr">
         <is>
-          <t>: もんだい5 この仕事が終わったら、(   )。</t>
+          <t>: もんだい5もし彼が来たら、私はすぐに (   )。</t>
         </is>
       </c>
       <c r="C43" s="1" t="inlineStr">
         <is>
-          <t>1. 帰ります 2. 休みます 3. 昼ご飯を食べます 4. 散歩します</t>
+          <t>1. 行きます 2. 準備します 3. 話します 4. 迎えます</t>
         </is>
       </c>
       <c r="D43" s="1" t="inlineStr">
@@ -1478,12 +1475,12 @@
       </c>
       <c r="B44" s="1" t="inlineStr">
         <is>
-          <t>: もんだい5 時間があったら、映画を (   )。</t>
+          <t>: もんだい5この仕事が終わったら、(   )。</t>
         </is>
       </c>
       <c r="C44" s="1" t="inlineStr">
         <is>
-          <t>1. 見ます 2. 読みます 3. 書きます 4. 聞きます</t>
+          <t>1. 帰ります 2. 休みます 3. 昼ご飯を食べます 4. 散歩します</t>
         </is>
       </c>
       <c r="D44" s="1" t="inlineStr">
@@ -1502,12 +1499,12 @@
       </c>
       <c r="B45" s="1" t="inlineStr">
         <is>
-          <t>: もんだい5 彼女が手伝ったら、もっと早く (   )。</t>
+          <t>: もんだい5時間があったら、映画を (   )。</t>
         </is>
       </c>
       <c r="C45" s="1" t="inlineStr">
         <is>
-          <t>1. 終わります 2. 始めます 3. 続けます 4. 休みます</t>
+          <t>1. 見ます 2. 読みます 3. 書きます 4. 聞きます</t>
         </is>
       </c>
       <c r="D45" s="1" t="inlineStr">
@@ -1526,12 +1523,12 @@
       </c>
       <c r="B46" s="1" t="inlineStr">
         <is>
-          <t>: もんだい5 この本を読んだら、次に何を (   )。</t>
+          <t>: もんだい5彼女が手伝ったら、もっと早く (   )。</t>
         </is>
       </c>
       <c r="C46" s="1" t="inlineStr">
         <is>
-          <t>1. 読みますか 2. 書きますか 3. 聞きますか 4. 見ますか</t>
+          <t>1. 終わります 2. 始めます 3. 続けます 4. 休みます</t>
         </is>
       </c>
       <c r="D46" s="1" t="inlineStr">
@@ -1550,12 +1547,12 @@
       </c>
       <c r="B47" s="1" t="inlineStr">
         <is>
-          <t>: もんだい5 友達が来たら、ゲームを一緒に (   )。</t>
+          <t>: もんだい5この本を読んだら、次に何を (   )。</t>
         </is>
       </c>
       <c r="C47" s="1" t="inlineStr">
         <is>
-          <t>1. します 2. 食べます 3. 聞きます 4. 見ます</t>
+          <t>1. 読みますか 2. 書きますか 3. 聞きますか 4. 見ますか</t>
         </is>
       </c>
       <c r="D47" s="1" t="inlineStr">
@@ -1574,12 +1571,12 @@
       </c>
       <c r="B48" s="1" t="inlineStr">
         <is>
-          <t>: もんだい5 電車が遅れたら、授業に (   )。</t>
+          <t>: もんだい5友達が来たら、ゲームを一緒に (   )。</t>
         </is>
       </c>
       <c r="C48" s="1" t="inlineStr">
         <is>
-          <t>1. 間に合いません 2. 遅れます 3. 行きません 4. 出ません</t>
+          <t>1. します 2. 食べます 3. 聞きます 4. 見ます</t>
         </is>
       </c>
       <c r="D48" s="1" t="inlineStr">
@@ -1598,12 +1595,12 @@
       </c>
       <c r="B49" s="1" t="inlineStr">
         <is>
-          <t>: もんだい5 もしお金がたくさんあったら、旅行に (   )。</t>
+          <t>: もんだい5電車が遅れたら、授業に (   )。</t>
         </is>
       </c>
       <c r="C49" s="1" t="inlineStr">
         <is>
-          <t>1. 行きたい 2. 買いたい 3. 住みたい 4. 食べたい</t>
+          <t>1. 間に合いません 2. 遅れます 3. 行きません 4. 出ません</t>
         </is>
       </c>
       <c r="D49" s="1" t="inlineStr">
@@ -1622,12 +1619,12 @@
       </c>
       <c r="B50" s="1" t="inlineStr">
         <is>
-          <t>: もんだい5 彼が答えたら、みんなが (   )。</t>
+          <t>: もんだい5もしお金がたくさんあったら、旅行に (   )。</t>
         </is>
       </c>
       <c r="C50" s="1" t="inlineStr">
         <is>
-          <t>1. 驚きます 2. 怒ります 3. 笑います 4. 泣きます</t>
+          <t>1. 行きたい 2. 買いたい 3. 住みたい 4. 食べたい</t>
         </is>
       </c>
       <c r="D50" s="1" t="inlineStr">
@@ -1646,12 +1643,12 @@
       </c>
       <c r="B51" s="1" t="inlineStr">
         <is>
-          <t>: もんだい6 A:「雨が降ったら、どうしますか。」 B:「雨が降ったら、家で映画を(   )。」</t>
+          <t>: もんだい5彼が答えたら、みんなが (   )。</t>
         </is>
       </c>
       <c r="C51" s="1" t="inlineStr">
         <is>
-          <t>1. 見ます 2. 読みます 3. 書きます 4. 食べます</t>
+          <t>1. 驚きます 2. 怒ります 3. 笑います 4. 泣きます</t>
         </is>
       </c>
       <c r="D51" s="1" t="inlineStr">
@@ -1670,12 +1667,12 @@
       </c>
       <c r="B52" s="1" t="inlineStr">
         <is>
-          <t>: もんだい6 A:「もし道に迷ったら、どうしますか。 」 B:「すぐにアプリで(   )。 」</t>
+          <t>: もんだい6A:「雨が降ったら、どうしますか。 」 B:「雨が降ったら、家で映画を(   )。 」</t>
         </is>
       </c>
       <c r="C52" s="1" t="inlineStr">
         <is>
-          <t>1. 調べます 2. 見つけます 3. 探します 4. 聞きます</t>
+          <t>1. 見ます 2. 読みます 3. 書きます 4. 食べます</t>
         </is>
       </c>
       <c r="D52" s="1" t="inlineStr">
@@ -1694,12 +1691,12 @@
       </c>
       <c r="B53" s="1" t="inlineStr">
         <is>
-          <t>: もんだい6 A:「テストが終わったら、何をしますか。 」 B:「終わったら、友達とカフェに(   )。 」</t>
+          <t>: もんだい6A:「もし道に迷ったら、どうしますか。 」 B:「すぐにアプリで(   )。 」</t>
         </is>
       </c>
       <c r="C53" s="1" t="inlineStr">
         <is>
-          <t>1. 行きます 2. 寝ます 3. 泳ぎます 4. 作ります</t>
+          <t>1. 調べます 2. 見つけます 3. 探します 4. 聞きます</t>
         </is>
       </c>
       <c r="D53" s="1" t="inlineStr">
@@ -1718,12 +1715,12 @@
       </c>
       <c r="B54" s="1" t="inlineStr">
         <is>
-          <t>: もんだい6 A:「明日暇(ひま)だったら、何をしますか。 」 B:「暇だったら、家でゆっくり(   )。 」</t>
+          <t>: もんだい6A:「テストが終わったら、何をしますか。 」 B:「終わったら、友達とカフェに(   )。 」</t>
         </is>
       </c>
       <c r="C54" s="1" t="inlineStr">
         <is>
-          <t>1. 休みます 2. 遊びます 3. 食べます 4. 読みます</t>
+          <t>1. 行きます 2. 寝ます 3. 泳ぎます 4. 作ります</t>
         </is>
       </c>
       <c r="D54" s="1" t="inlineStr">
@@ -1742,12 +1739,12 @@
       </c>
       <c r="B55" s="1" t="inlineStr">
         <is>
-          <t>: もんだい6 A:「もし、時間があったら、手伝ってもらえますか。 」 B:「時間があったら、もちろん(   )。 」</t>
+          <t>: もんだい6A:「明日暇(ひま)だったら、何をしますか。 」 B:「暇だったら、家でゆっくり(   )。 」</t>
         </is>
       </c>
       <c r="C55" s="1" t="inlineStr">
         <is>
-          <t>1. 手伝います 2. 泳ぎます 3. 書きます 4. 探します</t>
+          <t>1. 休みます 2. 遊びます 3. 食べます 4. 読みます</t>
         </is>
       </c>
       <c r="D55" s="1" t="inlineStr">
@@ -1766,12 +1763,12 @@
       </c>
       <c r="B56" s="1" t="inlineStr">
         <is>
-          <t>: もんだい6 A:「もし、今週末に予定がなかったら、どこに行きたいですか。 」 B:「予定がなかったら、海に(   )。 」</t>
+          <t>: もんだい6A:「もし、時間があったら、手伝ってもらえますか。 」 B:「時間があったら、もちろん(   )。 」</t>
         </is>
       </c>
       <c r="C56" s="1" t="inlineStr">
         <is>
-          <t>1. 行きたいです 2. 行きます 3. 行きました 4. 行ってください</t>
+          <t>1. 手伝います 2. 泳ぎます 3. 書きます 4. 探します</t>
         </is>
       </c>
       <c r="D56" s="1" t="inlineStr">
@@ -1790,12 +1787,12 @@
       </c>
       <c r="B57" s="1" t="inlineStr">
         <is>
-          <t>: もんだい6 A:「バスが遅れたら、どうしますか。 」 B:「遅れたら、タクシーを(   )。 」</t>
+          <t>: もんだい6A:「もし、今週末に予定がなかったら、どこに行きたいですか。 」 B:「予定がなかったら、海に(   )。 」</t>
         </is>
       </c>
       <c r="C57" s="1" t="inlineStr">
         <is>
-          <t>1. 使います 2. 乗ります 3. 買います 4. 売ります</t>
+          <t>1. 行きたいです 2. 行きます 3. 行きました 4. 行ってください</t>
         </is>
       </c>
       <c r="D57" s="1" t="inlineStr">
@@ -1814,12 +1811,12 @@
       </c>
       <c r="B58" s="1" t="inlineStr">
         <is>
-          <t>: もんだい6 A:「もし、財布を忘れたら、どうしますか。 」 B:「忘れたら、友達に(   )。 」</t>
+          <t>: もんだい6A:「バスが遅れたら、どうしますか。 」 B:「遅れたら、タクシーを(   )。 」</t>
         </is>
       </c>
       <c r="C58" s="1" t="inlineStr">
         <is>
-          <t>1. 借ります 2. 貸します 3. 聞きます 4. 言います</t>
+          <t>1. 使います 2. 乗ります 3. 買います 4. 売ります</t>
         </is>
       </c>
       <c r="D58" s="1" t="inlineStr">
@@ -1838,12 +1835,12 @@
       </c>
       <c r="B59" s="1" t="inlineStr">
         <is>
-          <t>: もんだい6 A:「もし、雨が降ったら、ピクニックはどうしますか。 」 B:「雨が降ったら、ピクニックは(   )。 」</t>
+          <t>: もんだい6A:「もし、財布を忘れたら、どうしますか。 」 B:「忘れたら、友達に(   )。 」</t>
         </is>
       </c>
       <c r="C59" s="1" t="inlineStr">
         <is>
-          <t>1. 中止します 2. します 3. 行います 4. 開きます</t>
+          <t>1. 借ります 2. 貸します 3. 聞きます 4. 言います</t>
         </is>
       </c>
       <c r="D59" s="1" t="inlineStr">
@@ -1862,12 +1859,12 @@
       </c>
       <c r="B60" s="1" t="inlineStr">
         <is>
-          <t>: もんだい6 A:「試験に合格したら、何をしますか。 」 B:「合格したら、家族と(   )。 」</t>
+          <t>: もんだい6A:「もし、雨が降ったら、ピクニックはどうしますか。 」 B:「雨が降ったら、ピクニックは(   )。 」</t>
         </is>
       </c>
       <c r="C60" s="1" t="inlineStr">
         <is>
-          <t>1. 祝います 2. 泣きます 3. 怒ります 4. 眠ります</t>
+          <t>1. 中止します 2. します 3. 行います 4. 開きます</t>
         </is>
       </c>
       <c r="D60" s="1" t="inlineStr">
@@ -1886,12 +1883,12 @@
       </c>
       <c r="B61" s="1" t="inlineStr">
         <is>
-          <t>: もんだい7 もし雨が降ったら、(   )。</t>
+          <t>: もんだい6A:「試験に合格したら、何をしますか。 」 B:「合格したら、家族と(   )。 」</t>
         </is>
       </c>
       <c r="C61" s="1" t="inlineStr">
         <is>
-          <t>1. 行きます 2. 行かない 3. 行こう 4. 行く</t>
+          <t>1. 祝います 2. 泣きます 3. 怒ります 4. 眠ります</t>
         </is>
       </c>
       <c r="D61" s="1" t="inlineStr">
@@ -1910,17 +1907,17 @@
       </c>
       <c r="B62" s="1" t="inlineStr">
         <is>
-          <t>: もんだい7 テストが 終わったら (   )。</t>
+          <t>: もんだい7もし 雨が 降ったら (   )。</t>
         </is>
       </c>
       <c r="C62" s="1" t="inlineStr">
         <is>
-          <t>1. 映画を見に行こう 2. 映画を見ない 3. 映画が見る 4. 映画を見た</t>
+          <t>1. 行ける 2. 行けない 3. 行こう 4. 行く</t>
         </is>
       </c>
       <c r="D62" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E62" s="1" t="inlineStr"/>
@@ -1934,12 +1931,12 @@
       </c>
       <c r="B63" s="1" t="inlineStr">
         <is>
-          <t>: もんだい7 もし お金が あったら、(   )。</t>
+          <t>: もんだい7テストが 終わったら (   )。</t>
         </is>
       </c>
       <c r="C63" s="1" t="inlineStr">
         <is>
-          <t>1. 旅行に行こう 2. 旅行に行く 3. 旅行に行かない 4. 旅行に行った</t>
+          <t>1. 映画を見に行こう 2. 映画を見ない 3. 映画が見る 4. 映画を見た</t>
         </is>
       </c>
       <c r="D63" s="1" t="inlineStr">
@@ -1958,17 +1955,17 @@
       </c>
       <c r="B64" s="1" t="inlineStr">
         <is>
-          <t>: もんだい7 時間が あったら (   )。</t>
+          <t>: もんだい7もし お金が あったら、(   )。</t>
         </is>
       </c>
       <c r="C64" s="1" t="inlineStr">
         <is>
-          <t>1. 勉強しない 2. 勉強しよう 3. 勉強ができる 4. 勉強することにした</t>
+          <t>1. 旅行に行こう 2. 旅行に行く 3. 旅行に行かない 4. 旅行に行った</t>
         </is>
       </c>
       <c r="D64" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E64" s="1" t="inlineStr"/>
@@ -1982,12 +1979,12 @@
       </c>
       <c r="B65" s="1" t="inlineStr">
         <is>
-          <t>: もんだい7 もし 彼が 来たら、(   )。</t>
+          <t>: もんだい7時間が あったら (   )。</t>
         </is>
       </c>
       <c r="C65" s="1" t="inlineStr">
         <is>
-          <t>1. 話しなかった 2. 話そう 3. 話せる 4. 話した</t>
+          <t>1. 勉強しない 2. 勉強しよう 3. 勉強ができる 4. 勉強することにした</t>
         </is>
       </c>
       <c r="D65" s="1" t="inlineStr">
@@ -2006,17 +2003,17 @@
       </c>
       <c r="B66" s="1" t="inlineStr">
         <is>
-          <t>: もんだい7 パーティーが 終わったら (   )。</t>
+          <t>: もんだい7もし 彼が 来たら、(   )。</t>
         </is>
       </c>
       <c r="C66" s="1" t="inlineStr">
         <is>
-          <t>1. 片付ける 2. 片付けない 3. 片付けよう 4. 片付けた</t>
+          <t>1. 話しなかった 2. 話そう 3. 話せる 4. 話した</t>
         </is>
       </c>
       <c r="D66" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E66" s="1" t="inlineStr"/>
@@ -2030,17 +2027,17 @@
       </c>
       <c r="B67" s="1" t="inlineStr">
         <is>
-          <t>: もんだい7 彼女が 行くと 言ったら、(   )。</t>
+          <t>: もんだい7パーティーが 終わったら (   )。</t>
         </is>
       </c>
       <c r="C67" s="1" t="inlineStr">
         <is>
-          <t>1. 行かないことにする 2. 行くことにした 3. 行こうと思った 4. 行くことができる</t>
+          <t>1. 片付ける 2. 片付けない 3. 片付けよう 4. 片付けた</t>
         </is>
       </c>
       <c r="D67" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E67" s="1" t="inlineStr"/>
@@ -2054,17 +2051,17 @@
       </c>
       <c r="B68" s="1" t="inlineStr">
         <is>
-          <t>: もんだい7 もし 道が わからなかったら、(   )。</t>
+          <t>: もんだい7彼女が 行くと 言ったら、(   )。</t>
         </is>
       </c>
       <c r="C68" s="1" t="inlineStr">
         <is>
-          <t>1. 聞こう 2. 聞かない 3. 聞ける 4. 聞いた</t>
+          <t>1. 行かないことにする 2. 行くことにした 3. 行こうと思った 4. 行くことができる</t>
         </is>
       </c>
       <c r="D68" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E68" s="1" t="inlineStr"/>
@@ -2078,12 +2075,12 @@
       </c>
       <c r="B69" s="1" t="inlineStr">
         <is>
-          <t>: もんだい7 天気が よかったら、(   )。</t>
+          <t>: もんだい7もし 道が わからなかったら、(   )。</t>
         </is>
       </c>
       <c r="C69" s="1" t="inlineStr">
         <is>
-          <t>1. ピクニックに行こう 2. ピクニックに行かない 3. ピクニックに行ける 4. ピクニックに行った</t>
+          <t>1. 聞こう 2. 聞かない 3. 聞ける 4. 聞いた</t>
         </is>
       </c>
       <c r="D69" s="1" t="inlineStr">
@@ -2102,17 +2099,17 @@
       </c>
       <c r="B70" s="1" t="inlineStr">
         <is>
-          <t>: もんだい7 先生が 来たら、(   )。</t>
+          <t>: もんだい7天気が よかったら、(   )。</t>
         </is>
       </c>
       <c r="C70" s="1" t="inlineStr">
         <is>
-          <t>1. 授業を始めた 2. 授業を始めよう 3. 授業を始めない 4. 授業が始める</t>
+          <t>1. ピクニックに行こう 2. ピクニックに行かない 3. ピクニックに行ける 4. ピクニックに行った</t>
         </is>
       </c>
       <c r="D70" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E70" s="1" t="inlineStr"/>
@@ -2126,12 +2123,12 @@
       </c>
       <c r="B71" s="1" t="inlineStr">
         <is>
-          <t>: もんだい8 雨が降ったら、試合は(   )中止(ちゅうし)になります。</t>
+          <t>: もんだい7先生が 来たら、(   )。</t>
         </is>
       </c>
       <c r="C71" s="1" t="inlineStr">
         <is>
-          <t>1. たぶん 2. きっと 3. ように 4. おそらく</t>
+          <t>1. 授業を始めた 2. 授業を始めよう 3. 授業を始めない 4. 授業が始める</t>
         </is>
       </c>
       <c r="D71" s="1" t="inlineStr">
@@ -2150,12 +2147,12 @@
       </c>
       <c r="B72" s="1" t="inlineStr">
         <is>
-          <t>: もんだい8 このケーキを食べたら、まるで天国(てんごく)にいる(   )美味(おい)しさです。</t>
+          <t>: もんだい8雨が降ったら、試合は(   )中止(ちゅうし)になります。</t>
         </is>
       </c>
       <c r="C72" s="1" t="inlineStr">
         <is>
-          <t>1. ような 2. らしい 3. ほど 4. みたいな</t>
+          <t>1. ように 2. みたいに 3. ほどに 4. らしく</t>
         </is>
       </c>
       <c r="D72" s="1" t="inlineStr">
@@ -2174,17 +2171,17 @@
       </c>
       <c r="B73" s="1" t="inlineStr">
         <is>
-          <t>: もんだい8 彼女(かのじょ)が来たら、部屋(へや)が明るくなった(   )感じ(かんじ)です。</t>
+          <t>: もんだい8このケーキを食べたら、まるで天国(てんごく)にいる(   )美味(おい)しさです。</t>
         </is>
       </c>
       <c r="C73" s="1" t="inlineStr">
         <is>
-          <t>1. みたいに 2. ように 3. ほどに 4. らしく</t>
+          <t>1. ような 2. らしい 3. ほど 4. みたいな</t>
         </is>
       </c>
       <c r="D73" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E73" s="1" t="inlineStr"/>
@@ -2198,17 +2195,17 @@
       </c>
       <c r="B74" s="1" t="inlineStr">
         <is>
-          <t>: もんだい8 食事(しょくじ)が終わったら、(   )映画(えいが)を見に行きましょう。</t>
+          <t>: もんだい8彼女(かのじょ)が来たら、部屋(へや)が明るくなった(   )感じ(かんじ)です。</t>
         </is>
       </c>
       <c r="C74" s="1" t="inlineStr">
         <is>
-          <t>1. ように 2. ほどに 3. みたいに 4. らしく</t>
+          <t>1. みたいに 2. ように 3. ほどに 4. らしく</t>
         </is>
       </c>
       <c r="D74" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E74" s="1" t="inlineStr"/>
@@ -2222,17 +2219,17 @@
       </c>
       <c r="B75" s="1" t="inlineStr">
         <is>
-          <t>: もんだい8 彼(かれ)の話(はなし)を聞いたら、夢(ゆめ)を見ている(   )気分(きぶん)になりました。</t>
+          <t>: もんだい8食事(しょくじ)が終わったら、(   )映画(えいが)を見に行きましょう。</t>
         </is>
       </c>
       <c r="C75" s="1" t="inlineStr">
         <is>
-          <t>1. らしい 2. ような 3. みたいな 4. ほど</t>
+          <t>1. ように 2. ほどに 3. みたいに 4. らしく</t>
         </is>
       </c>
       <c r="D75" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E75" s="1" t="inlineStr"/>
@@ -2246,12 +2243,12 @@
       </c>
       <c r="B76" s="1" t="inlineStr">
         <is>
-          <t>: もんだい8 お金(かね)があったら、まるで王様(おうさま)の(   )生活(せいかつ)ができるでしょう。</t>
+          <t>: もんだい8彼(かれ)の話(はなし)を聞いたら、夢(ゆめ)を見ている(   )気分(きぶん)になりました。</t>
         </is>
       </c>
       <c r="C76" s="1" t="inlineStr">
         <is>
-          <t>1. ほど 2. ような 3. みたいな 4. らしい</t>
+          <t>1. らしい 2. ような 3. みたいな 4. ほど</t>
         </is>
       </c>
       <c r="D76" s="1" t="inlineStr">
@@ -2270,12 +2267,12 @@
       </c>
       <c r="B77" s="1" t="inlineStr">
         <is>
-          <t>: もんだい8 宿題(しゅくだい)が終わったら、(   )遊(あそ)びに行けます。</t>
+          <t>: もんだい8お金(かね)があったら、まるで王様(おうさま)の(   )生活(せいかつ)ができるでしょう。</t>
         </is>
       </c>
       <c r="C77" s="1" t="inlineStr">
         <is>
-          <t>1. みたいに 2. ように 3. ほどに 4. らしく</t>
+          <t>1. ほど 2. ような 3. みたいな 4. らしい</t>
         </is>
       </c>
       <c r="D77" s="1" t="inlineStr">
@@ -2294,7 +2291,7 @@
       </c>
       <c r="B78" s="1" t="inlineStr">
         <is>
-          <t>: もんだい8 彼(かれ)は試験(しけん)に合格(ごうかく)したら、(   )喜(よろこ)びました。</t>
+          <t>: もんだい8宿題(しゅくだい)が終わったら、(   )遊(あそ)びに行けます。</t>
         </is>
       </c>
       <c r="C78" s="1" t="inlineStr">
@@ -2318,12 +2315,12 @@
       </c>
       <c r="B79" s="1" t="inlineStr">
         <is>
-          <t>: もんだい8 もし雨(あめ)が降ったら、(   )家(いえ)に帰(かえ)ります。</t>
+          <t>: もんだい8彼(かれ)は試験(しけん)に合格(ごうかく)したら、(   )喜(よろこ)びました。</t>
         </is>
       </c>
       <c r="C79" s="1" t="inlineStr">
         <is>
-          <t>1. ほどに 2. ように 3. みたいに 4. らしく</t>
+          <t>1. みたいに 2. ように 3. ほどに 4. らしく</t>
         </is>
       </c>
       <c r="D79" s="1" t="inlineStr">
@@ -2342,25 +2339,49 @@
       </c>
       <c r="B80" s="1" t="inlineStr">
         <is>
-          <t>: もんだい8 彼女(かのじょ)が笑(わら)ったら、太陽(たいよう)が輝(かがや)く(   )明(あか)るいです。</t>
+          <t>: もんだい8もし雨(あめ)が降ったら、(   )家(いえ)に帰(かえ)ります。</t>
         </is>
       </c>
       <c r="C80" s="1" t="inlineStr">
         <is>
-          <t>1. ように 2. みたいに 3. ほどに 4. らしく</t>
+          <t>1. ほどに 2. ように 3. みたいに 4. らしく</t>
         </is>
       </c>
       <c r="D80" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E80" s="1" t="inlineStr"/>
       <c r="F80" s="1" t="inlineStr"/>
     </row>
+    <row r="81">
+      <c r="A81" s="1" t="inlineStr">
+        <is>
+          <t>Q10</t>
+        </is>
+      </c>
+      <c r="B81" s="1" t="inlineStr">
+        <is>
+          <t>: もんだい8彼女(かのじょ)が笑(わら)ったら、太陽(たいよう)が輝(かがや)く(   )明(あか)るいです。</t>
+        </is>
+      </c>
+      <c r="C81" s="1" t="inlineStr">
+        <is>
+          <t>1. ように 2. みたいに 3. ほどに 4. らしく</t>
+        </is>
+      </c>
+      <c r="D81" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E81" s="1" t="inlineStr"/>
+      <c r="F81" s="1" t="inlineStr"/>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="E2:E80" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E2:E81" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"High_Q,Low_Q,Drop,Minor changes"</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/revised_shatin/qwen3-next-80b-a3b-thinking/test_grammar_3_['No. 23_～たら〈条件(じょうけん)〉 ']_revised_revised.xlsx
+++ b/docs/revised_shatin/qwen3-next-80b-a3b-thinking/test_grammar_3_['No. 23_～たら〈条件(じょうけん)〉 ']_revised_revised.xlsx
@@ -707,7 +707,7 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>: もんだい2雨が ふったら サッカーの試合は 中止 (   ) なる。</t>
+          <t>: もんだい2雨が　ふったら　サッカーの試合は　中止　(   )　なる。</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
@@ -731,7 +731,7 @@
       </c>
       <c r="B13" s="1" t="inlineStr">
         <is>
-          <t>: もんだい2このボタンを 押したら、ドアが (   )。</t>
+          <t>: もんだい2このボタンを　押したら、ドアが　(   )。</t>
         </is>
       </c>
       <c r="C13" s="1" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="B14" s="1" t="inlineStr">
         <is>
-          <t>: もんだい2友だちが 来たら いっしょ (   ) 食事を しましょう。</t>
+          <t>: もんだい2友だちが　来たら　いっしょ　(   )　食事を　しましょう。</t>
         </is>
       </c>
       <c r="C14" s="1" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="B15" s="1" t="inlineStr">
         <is>
-          <t>: もんだい2かぜを ひいたら、早く 寝る (   ) いいですよ。</t>
+          <t>: もんだい2かぜを　ひいたら、早く　寝る　(   )　いいですよ。</t>
         </is>
       </c>
       <c r="C15" s="1" t="inlineStr">
@@ -803,7 +803,7 @@
       </c>
       <c r="B16" s="1" t="inlineStr">
         <is>
-          <t>: もんだい2お金を ためたら、新しい パソコン (   ) 買うつもりです。</t>
+          <t>: もんだい2お金を　ためたら、新しい　パソコン　(   )　買うつもりです。</t>
         </is>
       </c>
       <c r="C16" s="1" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="B17" s="1" t="inlineStr">
         <is>
-          <t>: もんだい2駅に 着いたら 電話 (   ) ください。</t>
+          <t>: もんだい2駅に　着いたら　電話　(   )　ください。</t>
         </is>
       </c>
       <c r="C17" s="1" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="B18" s="1" t="inlineStr">
         <is>
-          <t>: もんだい2もし、彼に 会えたら、この 手紙を (   )。</t>
+          <t>: もんだい2もし、彼に　会えたら、この　手紙を　(   )。</t>
         </is>
       </c>
       <c r="C18" s="1" t="inlineStr">
@@ -875,7 +875,7 @@
       </c>
       <c r="B19" s="1" t="inlineStr">
         <is>
-          <t>: もんだい2宿題が 終わったら、遊びに (   ) 行きましょう。</t>
+          <t>: もんだい2宿題が　終わったら、遊びに　(   )　行きましょう。</t>
         </is>
       </c>
       <c r="C19" s="1" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="B20" s="1" t="inlineStr">
         <is>
-          <t>: もんだい2天気が よかったら、明日 (   ) 行きます。</t>
+          <t>: もんだい2天気が　よかったら、明日　(   )　行きます。</t>
         </is>
       </c>
       <c r="C20" s="1" t="inlineStr">
@@ -923,7 +923,7 @@
       </c>
       <c r="B21" s="1" t="inlineStr">
         <is>
-          <t>: もんだい2時間が あったら、映画を (   ) 見に行きます。</t>
+          <t>: もんだい2時間が　あったら、映画を　(   )　見に行きます。</t>
         </is>
       </c>
       <c r="C21" s="1" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="B32" s="1" t="inlineStr">
         <is>
-          <t>: もんだい4もし お金が たくさん あったら、 新しい車を (   ).</t>
+          <t>: もんだい4もし　お金が　たくさん　あったら、　新しい車を　(   ).</t>
         </is>
       </c>
       <c r="C32" s="1" t="inlineStr">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="B33" s="1" t="inlineStr">
         <is>
-          <t>: もんだい4もし 雨が 降ったら、 試合は (   ).</t>
+          <t>: もんだい4もし　雨が　降ったら、　試合は　(   ).</t>
         </is>
       </c>
       <c r="C33" s="1" t="inlineStr">
@@ -1235,7 +1235,7 @@
       </c>
       <c r="B34" s="1" t="inlineStr">
         <is>
-          <t>: もんだい4試験が 終わったら、 わたしは 映画を 見に行く (   ).</t>
+          <t>: もんだい4試験が　終わったら、　わたしは　映画を　見に行く　(   ).</t>
         </is>
       </c>
       <c r="C34" s="1" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="B35" s="1" t="inlineStr">
         <is>
-          <t>: もんだい4もし 暇だったら、 手伝いに (   ).</t>
+          <t>: もんだい4もし　暇だったら、　手伝いに　(   ).</t>
         </is>
       </c>
       <c r="C35" s="1" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="B36" s="1" t="inlineStr">
         <is>
-          <t>: もんだい4もし 時間が あったら、 新しいレストランで 食事を (   ).</t>
+          <t>: もんだい4もし　時間が　あったら、　新しいレストランで　食事を　(   ).</t>
         </is>
       </c>
       <c r="C36" s="1" t="inlineStr">
@@ -1307,7 +1307,7 @@
       </c>
       <c r="B37" s="1" t="inlineStr">
         <is>
-          <t>: もんだい4仕事が 終わったら、 友だちと カフェに (   ).</t>
+          <t>: もんだい4仕事が　終わったら、　友だちと　カフェに　(   ).</t>
         </is>
       </c>
       <c r="C37" s="1" t="inlineStr">
@@ -1331,7 +1331,7 @@
       </c>
       <c r="B38" s="1" t="inlineStr">
         <is>
-          <t>: もんだい4もし 試験に 合格したら、 旅行に (   ).</t>
+          <t>: もんだい4もし　試験に　合格したら、　旅行に　(   ).</t>
         </is>
       </c>
       <c r="C38" s="1" t="inlineStr">
@@ -1355,7 +1355,7 @@
       </c>
       <c r="B39" s="1" t="inlineStr">
         <is>
-          <t>: もんだい4もし 彼が 来たら、 お祝いを (   ).</t>
+          <t>: もんだい4もし　彼が　来たら、　お祝いを　(   ).</t>
         </is>
       </c>
       <c r="C39" s="1" t="inlineStr">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="B40" s="1" t="inlineStr">
         <is>
-          <t>: もんだい4もし 間違えたら、 すぐに 先生に (   ).</t>
+          <t>: もんだい4もし　間違えたら、　すぐに　先生に　(   ).</t>
         </is>
       </c>
       <c r="C40" s="1" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="B41" s="1" t="inlineStr">
         <is>
-          <t>: もんだい4もし 彼女が 行かないなら、 わたしも 行かない (   ).</t>
+          <t>: もんだい4もし　彼女が　行かないなら、　わたしも　行かない　(   ).</t>
         </is>
       </c>
       <c r="C41" s="1" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="B42" s="1" t="inlineStr">
         <is>
-          <t>: もんだい5雨が降ったら、試合は (   )。</t>
+          <t>: もんだい5雨が降ったら、試合は　(   )。</t>
         </is>
       </c>
       <c r="C42" s="1" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="B43" s="1" t="inlineStr">
         <is>
-          <t>: もんだい5もし彼が来たら、私はすぐに (   )。</t>
+          <t>: もんだい5もし彼が来たら、私はすぐに　(   )。</t>
         </is>
       </c>
       <c r="C43" s="1" t="inlineStr">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="B45" s="1" t="inlineStr">
         <is>
-          <t>: もんだい5時間があったら、映画を (   )。</t>
+          <t>: もんだい5時間があったら、映画を　(   )。</t>
         </is>
       </c>
       <c r="C45" s="1" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="B46" s="1" t="inlineStr">
         <is>
-          <t>: もんだい5彼女が手伝ったら、もっと早く (   )。</t>
+          <t>: もんだい5彼女が手伝ったら、もっと早く　(   )。</t>
         </is>
       </c>
       <c r="C46" s="1" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="B47" s="1" t="inlineStr">
         <is>
-          <t>: もんだい5この本を読んだら、次に何を (   )。</t>
+          <t>: もんだい5この本を読んだら、次に何を　(   )。</t>
         </is>
       </c>
       <c r="C47" s="1" t="inlineStr">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="B48" s="1" t="inlineStr">
         <is>
-          <t>: もんだい5友達が来たら、ゲームを一緒に (   )。</t>
+          <t>: もんだい5友達が来たら、ゲームを一緒に　(   )。</t>
         </is>
       </c>
       <c r="C48" s="1" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="B49" s="1" t="inlineStr">
         <is>
-          <t>: もんだい5電車が遅れたら、授業に (   )。</t>
+          <t>: もんだい5電車が遅れたら、授業に　(   )。</t>
         </is>
       </c>
       <c r="C49" s="1" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="B50" s="1" t="inlineStr">
         <is>
-          <t>: もんだい5もしお金がたくさんあったら、旅行に (   )。</t>
+          <t>: もんだい5もしお金がたくさんあったら、旅行に　(   )。</t>
         </is>
       </c>
       <c r="C50" s="1" t="inlineStr">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="B51" s="1" t="inlineStr">
         <is>
-          <t>: もんだい5彼が答えたら、みんなが (   )。</t>
+          <t>: もんだい5彼が答えたら、みんなが　(   )。</t>
         </is>
       </c>
       <c r="C51" s="1" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="B62" s="1" t="inlineStr">
         <is>
-          <t>: もんだい7もし 雨が 降ったら (   )。</t>
+          <t>: もんだい7もし　雨が　降ったら　(   )。</t>
         </is>
       </c>
       <c r="C62" s="1" t="inlineStr">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="B63" s="1" t="inlineStr">
         <is>
-          <t>: もんだい7テストが 終わったら (   )。</t>
+          <t>: もんだい7テストが　終わったら　(   )。</t>
         </is>
       </c>
       <c r="C63" s="1" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B64" s="1" t="inlineStr">
         <is>
-          <t>: もんだい7もし お金が あったら、(   )。</t>
+          <t>: もんだい7もし　お金が　あったら、(   )。</t>
         </is>
       </c>
       <c r="C64" s="1" t="inlineStr">
@@ -1979,7 +1979,7 @@
       </c>
       <c r="B65" s="1" t="inlineStr">
         <is>
-          <t>: もんだい7時間が あったら (   )。</t>
+          <t>: もんだい7時間が　あったら　(   )。</t>
         </is>
       </c>
       <c r="C65" s="1" t="inlineStr">
@@ -2003,7 +2003,7 @@
       </c>
       <c r="B66" s="1" t="inlineStr">
         <is>
-          <t>: もんだい7もし 彼が 来たら、(   )。</t>
+          <t>: もんだい7もし　彼が　来たら、(   )。</t>
         </is>
       </c>
       <c r="C66" s="1" t="inlineStr">
@@ -2027,7 +2027,7 @@
       </c>
       <c r="B67" s="1" t="inlineStr">
         <is>
-          <t>: もんだい7パーティーが 終わったら (   )。</t>
+          <t>: もんだい7パーティーが　終わったら　(   )。</t>
         </is>
       </c>
       <c r="C67" s="1" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="B68" s="1" t="inlineStr">
         <is>
-          <t>: もんだい7彼女が 行くと 言ったら、(   )。</t>
+          <t>: もんだい7彼女が　行くと　言ったら、(   )。</t>
         </is>
       </c>
       <c r="C68" s="1" t="inlineStr">
@@ -2075,7 +2075,7 @@
       </c>
       <c r="B69" s="1" t="inlineStr">
         <is>
-          <t>: もんだい7もし 道が わからなかったら、(   )。</t>
+          <t>: もんだい7もし　道が　わからなかったら、(   )。</t>
         </is>
       </c>
       <c r="C69" s="1" t="inlineStr">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="B70" s="1" t="inlineStr">
         <is>
-          <t>: もんだい7天気が よかったら、(   )。</t>
+          <t>: もんだい7天気が　よかったら、(   )。</t>
         </is>
       </c>
       <c r="C70" s="1" t="inlineStr">
@@ -2123,7 +2123,7 @@
       </c>
       <c r="B71" s="1" t="inlineStr">
         <is>
-          <t>: もんだい7先生が 来たら、(   )。</t>
+          <t>: もんだい7先生が　来たら、(   )。</t>
         </is>
       </c>
       <c r="C71" s="1" t="inlineStr">
